--- a/VerveStacks_NOR_grids_kan10/vt_vervestacks_NOR_v1.xlsx
+++ b/VerveStacks_NOR_grids_kan10/vt_vervestacks_NOR_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D12A4017-A1ED-4BFF-B1F9-FA7D68441568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8AC36BC9-02D3-4F5B-8A09-8D6E3F1C2415}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{69451372-92E9-4966-9F9E-93567B86906F}"/>
+    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="12682" xr2:uid="{44D92771-AEB0-418D-A1D1-AEBBE65F955A}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1663,7 +1663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489215B4-19AD-4B28-8377-14139FE6E108}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3306E47-D93C-4261-8509-B680956102AB}">
   <dimension ref="B9:V14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1991,7 +1991,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52738B9C-1D6B-48FD-949A-072081C00508}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7BBFF9F6-2464-4367-8A1F-5B167C8C46EC}">
   <dimension ref="B9:W33"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3319,7 +3319,7 @@
         <v>30</v>
       </c>
       <c r="N31">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
       <c r="P31" t="s">
         <v>223</v>
@@ -3473,7 +3473,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BD51C13-2EBE-4C04-99A5-72D0402DDABF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1AEF2F72-8E58-4B38-AB2B-8885E955AAED}">
   <dimension ref="B9:W260"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -12838,7 +12838,7 @@
         <v>15</v>
       </c>
       <c r="S169" t="s">
-        <v>336</v>
+        <v>235</v>
       </c>
       <c r="T169" t="s">
         <v>225</v>
@@ -12897,7 +12897,7 @@
         <v>15</v>
       </c>
       <c r="S170" t="s">
-        <v>235</v>
+        <v>336</v>
       </c>
       <c r="T170" t="s">
         <v>225</v>
@@ -16054,7 +16054,7 @@
         <v>49</v>
       </c>
       <c r="N253">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
     </row>
     <row r="254" spans="2:14" x14ac:dyDescent="0.45">
@@ -16092,7 +16092,7 @@
         <v>43</v>
       </c>
       <c r="N254">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
     </row>
     <row r="255" spans="2:14" x14ac:dyDescent="0.45">
@@ -16130,7 +16130,7 @@
         <v>41</v>
       </c>
       <c r="N255">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
     </row>
     <row r="256" spans="2:14" x14ac:dyDescent="0.45">
@@ -16168,7 +16168,7 @@
         <v>40</v>
       </c>
       <c r="N256">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
     </row>
     <row r="257" spans="2:14" x14ac:dyDescent="0.45">
@@ -16206,7 +16206,7 @@
         <v>38</v>
       </c>
       <c r="N257">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
     </row>
     <row r="258" spans="2:14" x14ac:dyDescent="0.45">
@@ -16244,7 +16244,7 @@
         <v>36</v>
       </c>
       <c r="N258">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
     </row>
     <row r="259" spans="2:14" x14ac:dyDescent="0.45">
@@ -16282,7 +16282,7 @@
         <v>33</v>
       </c>
       <c r="N259">
-        <v>0.31985720347177776</v>
+        <v>0.31985720347177771</v>
       </c>
     </row>
     <row r="260" spans="2:14" x14ac:dyDescent="0.45">
@@ -16311,7 +16311,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{348C4D98-6A9C-4D4D-92F6-C24C77546DC8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E84C1AD-E065-4BC3-B59D-3E927A591FD2}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
